--- a/design/tables/Decoration.xlsx
+++ b/design/tables/Decoration.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Decoration" sheetId="1" r:id="R526d9456f20d46a2"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Decoration" sheetId="1" r:id="R1f7bf541f9154f57"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -1902,6 +1902,188 @@
         <x:v>6</x:v>
       </x:c>
     </x:row>
+    <x:row r="63">
+      <x:c r="A63" t="n">
+        <x:v>58</x:v>
+      </x:c>
+      <x:c r="B63" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C63" t="str">
+        <x:v>planter</x:v>
+      </x:c>
+      <x:c r="D63" t="n">
+        <x:v>104</x:v>
+      </x:c>
+      <x:c r="E63" t="n">
+        <x:v>116</x:v>
+      </x:c>
+      <x:c r="F63" t="n">
+        <x:v>48</x:v>
+      </x:c>
+      <x:c r="G63" t="n">
+        <x:v>48</x:v>
+      </x:c>
+      <x:c r="H63" t="n">
+        <x:v>4</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="64">
+      <x:c r="A64" t="n">
+        <x:v>59</x:v>
+      </x:c>
+      <x:c r="B64" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C64" t="str">
+        <x:v>tree</x:v>
+      </x:c>
+      <x:c r="D64" t="n">
+        <x:v>310</x:v>
+      </x:c>
+      <x:c r="E64" t="n">
+        <x:v>119</x:v>
+      </x:c>
+      <x:c r="F64" t="n">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="G64" t="n">
+        <x:v>56</x:v>
+      </x:c>
+      <x:c r="H64" t="n">
+        <x:v>4</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="65">
+      <x:c r="A65" t="n">
+        <x:v>60</x:v>
+      </x:c>
+      <x:c r="B65" t="n">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="C65" t="str">
+        <x:v>tree</x:v>
+      </x:c>
+      <x:c r="D65" t="n">
+        <x:v>64</x:v>
+      </x:c>
+      <x:c r="E65" t="n">
+        <x:v>550</x:v>
+      </x:c>
+      <x:c r="F65" t="n">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="G65" t="n">
+        <x:v>56</x:v>
+      </x:c>
+      <x:c r="H65" t="n">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="66">
+      <x:c r="A66" t="n">
+        <x:v>61</x:v>
+      </x:c>
+      <x:c r="B66" t="n">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="C66" t="str">
+        <x:v>planter</x:v>
+      </x:c>
+      <x:c r="D66" t="n">
+        <x:v>116</x:v>
+      </x:c>
+      <x:c r="E66" t="n">
+        <x:v>554</x:v>
+      </x:c>
+      <x:c r="F66" t="n">
+        <x:v>48</x:v>
+      </x:c>
+      <x:c r="G66" t="n">
+        <x:v>48</x:v>
+      </x:c>
+      <x:c r="H66" t="n">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="67">
+      <x:c r="A67" t="n">
+        <x:v>62</x:v>
+      </x:c>
+      <x:c r="B67" t="n">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="C67" t="str">
+        <x:v>tree</x:v>
+      </x:c>
+      <x:c r="D67" t="n">
+        <x:v>352</x:v>
+      </x:c>
+      <x:c r="E67" t="n">
+        <x:v>370</x:v>
+      </x:c>
+      <x:c r="F67" t="n">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="G67" t="n">
+        <x:v>56</x:v>
+      </x:c>
+      <x:c r="H67" t="n">
+        <x:v>2</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="68">
+      <x:c r="A68" t="n">
+        <x:v>63</x:v>
+      </x:c>
+      <x:c r="B68" t="n">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="C68" t="str">
+        <x:v>planter</x:v>
+      </x:c>
+      <x:c r="D68" t="n">
+        <x:v>352</x:v>
+      </x:c>
+      <x:c r="E68" t="n">
+        <x:v>434</x:v>
+      </x:c>
+      <x:c r="F68" t="n">
+        <x:v>48</x:v>
+      </x:c>
+      <x:c r="G68" t="n">
+        <x:v>48</x:v>
+      </x:c>
+      <x:c r="H68" t="n">
+        <x:v>2</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="69">
+      <x:c r="A69" t="n">
+        <x:v>64</x:v>
+      </x:c>
+      <x:c r="B69" t="n">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="C69" t="str">
+        <x:v>tree</x:v>
+      </x:c>
+      <x:c r="D69" t="n">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="E69" t="n">
+        <x:v>212</x:v>
+      </x:c>
+      <x:c r="F69" t="n">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="G69" t="n">
+        <x:v>56</x:v>
+      </x:c>
+      <x:c r="H69" t="n">
+        <x:v>3</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>

--- a/design/tables/Decoration.xlsx
+++ b/design/tables/Decoration.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Decoration" sheetId="1" r:id="R1f7bf541f9154f57"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Decoration" sheetId="1" r:id="R372ba71c7891410a"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -431,10 +431,10 @@
         <x:v>tree</x:v>
       </x:c>
       <x:c r="D6" s="7" t="n">
-        <x:v>196</x:v>
+        <x:v>200</x:v>
       </x:c>
       <x:c r="E6" s="7" t="n">
-        <x:v>128</x:v>
+        <x:v>125</x:v>
       </x:c>
       <x:c r="F6" s="7" t="n">
         <x:v>40</x:v>
@@ -457,10 +457,10 @@
         <x:v>planter</x:v>
       </x:c>
       <x:c r="D7" s="7" t="n">
-        <x:v>248</x:v>
+        <x:v>260</x:v>
       </x:c>
       <x:c r="E7" s="7" t="n">
-        <x:v>132</x:v>
+        <x:v>135</x:v>
       </x:c>
       <x:c r="F7" s="7" t="n">
         <x:v>48</x:v>
@@ -486,7 +486,7 @@
         <x:v>30</x:v>
       </x:c>
       <x:c r="E8" s="7" t="n">
-        <x:v>298</x:v>
+        <x:v>295</x:v>
       </x:c>
       <x:c r="F8" s="7" t="n">
         <x:v>40</x:v>
@@ -509,10 +509,10 @@
         <x:v>planter</x:v>
       </x:c>
       <x:c r="D9" s="7" t="n">
-        <x:v>354</x:v>
+        <x:v>350</x:v>
       </x:c>
       <x:c r="E9" s="7" t="n">
-        <x:v>484</x:v>
+        <x:v>275</x:v>
       </x:c>
       <x:c r="F9" s="7" t="n">
         <x:v>48</x:v>
@@ -535,10 +535,10 @@
         <x:v>tree</x:v>
       </x:c>
       <x:c r="D10" s="7" t="n">
-        <x:v>54</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="E10" s="7" t="n">
-        <x:v>526</x:v>
+        <x:v>525</x:v>
       </x:c>
       <x:c r="F10" s="7" t="n">
         <x:v>40</x:v>
@@ -561,10 +561,10 @@
         <x:v>planter</x:v>
       </x:c>
       <x:c r="D11" s="7" t="n">
-        <x:v>106</x:v>
+        <x:v>110</x:v>
       </x:c>
       <x:c r="E11" s="7" t="n">
-        <x:v>530</x:v>
+        <x:v>525</x:v>
       </x:c>
       <x:c r="F11" s="7" t="n">
         <x:v>48</x:v>
@@ -587,10 +587,10 @@
         <x:v>tree</x:v>
       </x:c>
       <x:c r="D12" s="7" t="n">
-        <x:v>352</x:v>
+        <x:v>170</x:v>
       </x:c>
       <x:c r="E12" s="7" t="n">
-        <x:v>380</x:v>
+        <x:v>505</x:v>
       </x:c>
       <x:c r="F12" s="7" t="n">
         <x:v>40</x:v>
@@ -613,10 +613,10 @@
         <x:v>planter</x:v>
       </x:c>
       <x:c r="D13" s="7" t="n">
-        <x:v>352</x:v>
+        <x:v>190</x:v>
       </x:c>
       <x:c r="E13" s="7" t="n">
-        <x:v>442</x:v>
+        <x:v>575</x:v>
       </x:c>
       <x:c r="F13" s="7" t="n">
         <x:v>48</x:v>
@@ -639,10 +639,10 @@
         <x:v>planter</x:v>
       </x:c>
       <x:c r="D14" s="7" t="n">
-        <x:v>354</x:v>
+        <x:v>350</x:v>
       </x:c>
       <x:c r="E14" s="7" t="n">
-        <x:v>108</x:v>
+        <x:v>105</x:v>
       </x:c>
       <x:c r="F14" s="7" t="n">
         <x:v>48</x:v>
@@ -665,10 +665,10 @@
         <x:v>planter</x:v>
       </x:c>
       <x:c r="D15" s="7" t="n">
-        <x:v>36</x:v>
+        <x:v>240</x:v>
       </x:c>
       <x:c r="E15" s="7" t="n">
-        <x:v>576</x:v>
+        <x:v>575</x:v>
       </x:c>
       <x:c r="F15" s="7" t="n">
         <x:v>48</x:v>
@@ -691,10 +691,10 @@
         <x:v>tree</x:v>
       </x:c>
       <x:c r="D16" s="7" t="n">
-        <x:v>56</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="E16" s="7" t="n">
-        <x:v>528</x:v>
+        <x:v>525</x:v>
       </x:c>
       <x:c r="F16" s="7" t="n">
         <x:v>40</x:v>
@@ -717,10 +717,10 @@
         <x:v>planter</x:v>
       </x:c>
       <x:c r="D17" s="7" t="n">
-        <x:v>108</x:v>
+        <x:v>120</x:v>
       </x:c>
       <x:c r="E17" s="7" t="n">
-        <x:v>532</x:v>
+        <x:v>535</x:v>
       </x:c>
       <x:c r="F17" s="7" t="n">
         <x:v>48</x:v>
@@ -743,10 +743,10 @@
         <x:v>tree</x:v>
       </x:c>
       <x:c r="D18" s="7" t="n">
-        <x:v>352</x:v>
+        <x:v>350</x:v>
       </x:c>
       <x:c r="E18" s="7" t="n">
-        <x:v>370</x:v>
+        <x:v>125</x:v>
       </x:c>
       <x:c r="F18" s="7" t="n">
         <x:v>40</x:v>
@@ -769,10 +769,10 @@
         <x:v>planter</x:v>
       </x:c>
       <x:c r="D19" s="7" t="n">
-        <x:v>352</x:v>
+        <x:v>170</x:v>
       </x:c>
       <x:c r="E19" s="7" t="n">
-        <x:v>438</x:v>
+        <x:v>565</x:v>
       </x:c>
       <x:c r="F19" s="7" t="n">
         <x:v>48</x:v>
@@ -795,10 +795,10 @@
         <x:v>tree</x:v>
       </x:c>
       <x:c r="D20" s="7" t="n">
-        <x:v>64</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="E20" s="7" t="n">
-        <x:v>550</x:v>
+        <x:v>545</x:v>
       </x:c>
       <x:c r="F20" s="7" t="n">
         <x:v>40</x:v>
@@ -821,10 +821,10 @@
         <x:v>planter</x:v>
       </x:c>
       <x:c r="D21" s="7" t="n">
-        <x:v>116</x:v>
+        <x:v>120</x:v>
       </x:c>
       <x:c r="E21" s="7" t="n">
-        <x:v>554</x:v>
+        <x:v>555</x:v>
       </x:c>
       <x:c r="F21" s="7" t="n">
         <x:v>48</x:v>
@@ -847,10 +847,10 @@
         <x:v>tree</x:v>
       </x:c>
       <x:c r="D22" s="7" t="n">
-        <x:v>354</x:v>
+        <x:v>350</x:v>
       </x:c>
       <x:c r="E22" s="7" t="n">
-        <x:v>142</x:v>
+        <x:v>145</x:v>
       </x:c>
       <x:c r="F22" s="7" t="n">
         <x:v>40</x:v>
@@ -873,10 +873,10 @@
         <x:v>planter</x:v>
       </x:c>
       <x:c r="D23" s="7" t="n">
-        <x:v>354</x:v>
+        <x:v>350</x:v>
       </x:c>
       <x:c r="E23" s="7" t="n">
-        <x:v>204</x:v>
+        <x:v>205</x:v>
       </x:c>
       <x:c r="F23" s="7" t="n">
         <x:v>48</x:v>
@@ -899,10 +899,10 @@
         <x:v>tree</x:v>
       </x:c>
       <x:c r="D24" s="7" t="n">
-        <x:v>52</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="E24" s="7" t="n">
-        <x:v>120</x:v>
+        <x:v>115</x:v>
       </x:c>
       <x:c r="F24" s="7" t="n">
         <x:v>40</x:v>
@@ -925,10 +925,10 @@
         <x:v>planter</x:v>
       </x:c>
       <x:c r="D25" s="7" t="n">
-        <x:v>104</x:v>
+        <x:v>110</x:v>
       </x:c>
       <x:c r="E25" s="7" t="n">
-        <x:v>124</x:v>
+        <x:v>125</x:v>
       </x:c>
       <x:c r="F25" s="7" t="n">
         <x:v>48</x:v>
@@ -951,10 +951,10 @@
         <x:v>tree</x:v>
       </x:c>
       <x:c r="D26" s="7" t="n">
-        <x:v>278</x:v>
+        <x:v>280</x:v>
       </x:c>
       <x:c r="E26" s="7" t="n">
-        <x:v>132</x:v>
+        <x:v>135</x:v>
       </x:c>
       <x:c r="F26" s="7" t="n">
         <x:v>40</x:v>
@@ -977,10 +977,10 @@
         <x:v>planter</x:v>
       </x:c>
       <x:c r="D27" s="7" t="n">
-        <x:v>330</x:v>
+        <x:v>340</x:v>
       </x:c>
       <x:c r="E27" s="7" t="n">
-        <x:v>136</x:v>
+        <x:v>135</x:v>
       </x:c>
       <x:c r="F27" s="7" t="n">
         <x:v>48</x:v>
@@ -1006,7 +1006,7 @@
         <x:v>30</x:v>
       </x:c>
       <x:c r="E28" s="7" t="n">
-        <x:v>360</x:v>
+        <x:v>575</x:v>
       </x:c>
       <x:c r="F28" s="7" t="n">
         <x:v>48</x:v>
@@ -1029,10 +1029,10 @@
         <x:v>tree</x:v>
       </x:c>
       <x:c r="D29" s="7" t="n">
-        <x:v>304</x:v>
+        <x:v>340</x:v>
       </x:c>
       <x:c r="E29" s="7" t="n">
-        <x:v>304</x:v>
+        <x:v>285</x:v>
       </x:c>
       <x:c r="F29" s="7" t="n">
         <x:v>40</x:v>
@@ -1055,10 +1055,10 @@
         <x:v>planter</x:v>
       </x:c>
       <x:c r="D30" s="7" t="n">
-        <x:v>356</x:v>
+        <x:v>360</x:v>
       </x:c>
       <x:c r="E30" s="7" t="n">
-        <x:v>308</x:v>
+        <x:v>225</x:v>
       </x:c>
       <x:c r="F30" s="7" t="n">
         <x:v>48</x:v>
@@ -1081,10 +1081,10 @@
         <x:v>tree</x:v>
       </x:c>
       <x:c r="D31" s="7" t="n">
-        <x:v>32</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="E31" s="7" t="n">
-        <x:v>484</x:v>
+        <x:v>485</x:v>
       </x:c>
       <x:c r="F31" s="7" t="n">
         <x:v>40</x:v>
@@ -1107,10 +1107,10 @@
         <x:v>planter</x:v>
       </x:c>
       <x:c r="D32" s="7" t="n">
-        <x:v>84</x:v>
+        <x:v>280</x:v>
       </x:c>
       <x:c r="E32" s="7" t="n">
-        <x:v>488</x:v>
+        <x:v>575</x:v>
       </x:c>
       <x:c r="F32" s="7" t="n">
         <x:v>48</x:v>
@@ -1133,10 +1133,10 @@
         <x:v>tree</x:v>
       </x:c>
       <x:c r="D33" s="7" t="n">
-        <x:v>64</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="E33" s="7" t="n">
-        <x:v>550</x:v>
+        <x:v>545</x:v>
       </x:c>
       <x:c r="F33" s="7" t="n">
         <x:v>40</x:v>
@@ -1159,10 +1159,10 @@
         <x:v>planter</x:v>
       </x:c>
       <x:c r="D34" s="7" t="n">
-        <x:v>116</x:v>
+        <x:v>120</x:v>
       </x:c>
       <x:c r="E34" s="7" t="n">
-        <x:v>554</x:v>
+        <x:v>555</x:v>
       </x:c>
       <x:c r="F34" s="7" t="n">
         <x:v>48</x:v>
@@ -1185,10 +1185,10 @@
         <x:v>tree</x:v>
       </x:c>
       <x:c r="D35" s="7" t="n">
-        <x:v>350</x:v>
+        <x:v>360</x:v>
       </x:c>
       <x:c r="E35" s="7" t="n">
-        <x:v>380</x:v>
+        <x:v>365</x:v>
       </x:c>
       <x:c r="F35" s="7" t="n">
         <x:v>40</x:v>
@@ -1211,10 +1211,10 @@
         <x:v>planter</x:v>
       </x:c>
       <x:c r="D36" s="7" t="n">
-        <x:v>354</x:v>
+        <x:v>130</x:v>
       </x:c>
       <x:c r="E36" s="7" t="n">
-        <x:v>444</x:v>
+        <x:v>145</x:v>
       </x:c>
       <x:c r="F36" s="7" t="n">
         <x:v>48</x:v>
@@ -1228,51 +1228,51 @@
     </x:row>
     <x:row r="37" ht="15" hidden="0" customHeight="1">
       <x:c r="A37" s="7" t="n">
-        <x:v>32</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="B37" s="7" t="n">
-        <x:v>8</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="C37" s="2" t="str">
-        <x:v>planter</x:v>
+        <x:v>tree</x:v>
       </x:c>
       <x:c r="D37" s="7" t="n">
-        <x:v>120</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="E37" s="7" t="n">
-        <x:v>120</x:v>
+        <x:v>545</x:v>
       </x:c>
       <x:c r="F37" s="7" t="n">
-        <x:v>48</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="G37" s="7" t="n">
-        <x:v>48</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="H37" s="7" t="n">
-        <x:v>3</x:v>
+        <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="38" ht="15" hidden="0" customHeight="1">
       <x:c r="A38" s="7" t="n">
-        <x:v>33</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="B38" s="7" t="n">
         <x:v>9</x:v>
       </x:c>
       <x:c r="C38" s="2" t="str">
-        <x:v>tree</x:v>
+        <x:v>planter</x:v>
       </x:c>
       <x:c r="D38" s="7" t="n">
-        <x:v>46</x:v>
+        <x:v>110</x:v>
       </x:c>
       <x:c r="E38" s="7" t="n">
-        <x:v>550</x:v>
+        <x:v>555</x:v>
       </x:c>
       <x:c r="F38" s="7" t="n">
-        <x:v>40</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="G38" s="7" t="n">
-        <x:v>56</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="H38" s="7" t="n">
         <x:v>1</x:v>
@@ -1280,51 +1280,51 @@
     </x:row>
     <x:row r="39" ht="15" hidden="0" customHeight="1">
       <x:c r="A39" s="7" t="n">
-        <x:v>34</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="B39" s="7" t="n">
         <x:v>9</x:v>
       </x:c>
       <x:c r="C39" s="2" t="str">
-        <x:v>planter</x:v>
+        <x:v>tree</x:v>
       </x:c>
       <x:c r="D39" s="7" t="n">
-        <x:v>98</x:v>
+        <x:v>330</x:v>
       </x:c>
       <x:c r="E39" s="7" t="n">
-        <x:v>554</x:v>
+        <x:v>365</x:v>
       </x:c>
       <x:c r="F39" s="7" t="n">
-        <x:v>48</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="G39" s="7" t="n">
-        <x:v>48</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="H39" s="7" t="n">
-        <x:v>1</x:v>
+        <x:v>2</x:v>
       </x:c>
     </x:row>
     <x:row r="40" ht="15" hidden="0" customHeight="1">
       <x:c r="A40" s="7" t="n">
-        <x:v>35</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="B40" s="7" t="n">
         <x:v>9</x:v>
       </x:c>
       <x:c r="C40" s="2" t="str">
-        <x:v>tree</x:v>
+        <x:v>planter</x:v>
       </x:c>
       <x:c r="D40" s="7" t="n">
         <x:v>330</x:v>
       </x:c>
       <x:c r="E40" s="7" t="n">
-        <x:v>370</x:v>
+        <x:v>435</x:v>
       </x:c>
       <x:c r="F40" s="7" t="n">
-        <x:v>40</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="G40" s="7" t="n">
-        <x:v>56</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="H40" s="7" t="n">
         <x:v>2</x:v>
@@ -1332,7 +1332,7 @@
     </x:row>
     <x:row r="41" ht="15" hidden="0" customHeight="1">
       <x:c r="A41" s="7" t="n">
-        <x:v>36</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="B41" s="7" t="n">
         <x:v>9</x:v>
@@ -1341,10 +1341,10 @@
         <x:v>planter</x:v>
       </x:c>
       <x:c r="D41" s="7" t="n">
-        <x:v>330</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="E41" s="7" t="n">
-        <x:v>432</x:v>
+        <x:v>195</x:v>
       </x:c>
       <x:c r="F41" s="7" t="n">
         <x:v>48</x:v>
@@ -1353,56 +1353,56 @@
         <x:v>48</x:v>
       </x:c>
       <x:c r="H41" s="7" t="n">
-        <x:v>2</x:v>
+        <x:v>3</x:v>
       </x:c>
     </x:row>
     <x:row r="42" ht="15" hidden="0" customHeight="1">
       <x:c r="A42" s="7" t="n">
-        <x:v>37</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="B42" s="7" t="n">
-        <x:v>9</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="C42" s="2" t="str">
-        <x:v>planter</x:v>
+        <x:v>tree</x:v>
       </x:c>
       <x:c r="D42" s="7" t="n">
-        <x:v>52</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="E42" s="7" t="n">
-        <x:v>196</x:v>
+        <x:v>545</x:v>
       </x:c>
       <x:c r="F42" s="7" t="n">
-        <x:v>48</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="G42" s="7" t="n">
-        <x:v>48</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="H42" s="7" t="n">
-        <x:v>3</x:v>
+        <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="43" ht="15" hidden="0" customHeight="1">
       <x:c r="A43" s="7" t="n">
-        <x:v>38</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="B43" s="7" t="n">
         <x:v>10</x:v>
       </x:c>
       <x:c r="C43" s="2" t="str">
-        <x:v>tree</x:v>
+        <x:v>planter</x:v>
       </x:c>
       <x:c r="D43" s="7" t="n">
-        <x:v>64</x:v>
+        <x:v>120</x:v>
       </x:c>
       <x:c r="E43" s="7" t="n">
-        <x:v>550</x:v>
+        <x:v>555</x:v>
       </x:c>
       <x:c r="F43" s="7" t="n">
-        <x:v>40</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="G43" s="7" t="n">
-        <x:v>56</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="H43" s="7" t="n">
         <x:v>1</x:v>
@@ -1410,51 +1410,51 @@
     </x:row>
     <x:row r="44" ht="15" hidden="0" customHeight="1">
       <x:c r="A44" s="7" t="n">
-        <x:v>39</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="B44" s="7" t="n">
         <x:v>10</x:v>
       </x:c>
       <x:c r="C44" s="2" t="str">
-        <x:v>planter</x:v>
+        <x:v>tree</x:v>
       </x:c>
       <x:c r="D44" s="7" t="n">
-        <x:v>116</x:v>
+        <x:v>170</x:v>
       </x:c>
       <x:c r="E44" s="7" t="n">
-        <x:v>554</x:v>
+        <x:v>525</x:v>
       </x:c>
       <x:c r="F44" s="7" t="n">
-        <x:v>48</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="G44" s="7" t="n">
-        <x:v>48</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="H44" s="7" t="n">
-        <x:v>1</x:v>
+        <x:v>2</x:v>
       </x:c>
     </x:row>
     <x:row r="45" ht="15" hidden="0" customHeight="1">
       <x:c r="A45" s="7" t="n">
-        <x:v>40</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="B45" s="7" t="n">
         <x:v>10</x:v>
       </x:c>
       <x:c r="C45" s="2" t="str">
-        <x:v>tree</x:v>
+        <x:v>planter</x:v>
       </x:c>
       <x:c r="D45" s="7" t="n">
-        <x:v>352</x:v>
+        <x:v>350</x:v>
       </x:c>
       <x:c r="E45" s="7" t="n">
-        <x:v>370</x:v>
+        <x:v>105</x:v>
       </x:c>
       <x:c r="F45" s="7" t="n">
-        <x:v>40</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="G45" s="7" t="n">
-        <x:v>56</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="H45" s="7" t="n">
         <x:v>2</x:v>
@@ -1462,51 +1462,51 @@
     </x:row>
     <x:row r="46" ht="15" hidden="0" customHeight="1">
       <x:c r="A46" s="7" t="n">
-        <x:v>41</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="B46" s="7" t="n">
         <x:v>10</x:v>
       </x:c>
       <x:c r="C46" s="2" t="str">
-        <x:v>planter</x:v>
+        <x:v>tree</x:v>
       </x:c>
       <x:c r="D46" s="7" t="n">
-        <x:v>352</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="E46" s="7" t="n">
-        <x:v>434</x:v>
+        <x:v>105</x:v>
       </x:c>
       <x:c r="F46" s="7" t="n">
-        <x:v>48</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="G46" s="7" t="n">
-        <x:v>48</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="H46" s="7" t="n">
-        <x:v>2</x:v>
+        <x:v>3</x:v>
       </x:c>
     </x:row>
     <x:row r="47" ht="15" hidden="0" customHeight="1">
       <x:c r="A47" s="7" t="n">
-        <x:v>42</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="B47" s="7" t="n">
-        <x:v>10</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="C47" s="2" t="str">
-        <x:v>tree</x:v>
+        <x:v>planter</x:v>
       </x:c>
       <x:c r="D47" s="7" t="n">
-        <x:v>52</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="E47" s="7" t="n">
-        <x:v>212</x:v>
+        <x:v>575</x:v>
       </x:c>
       <x:c r="F47" s="7" t="n">
-        <x:v>40</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="G47" s="7" t="n">
-        <x:v>56</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="H47" s="7" t="n">
         <x:v>3</x:v>
@@ -1514,25 +1514,25 @@
     </x:row>
     <x:row r="48" ht="15" hidden="0" customHeight="1">
       <x:c r="A48" s="7" t="n">
-        <x:v>43</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="B48" s="7" t="n">
         <x:v>11</x:v>
       </x:c>
       <x:c r="C48" s="2" t="str">
-        <x:v>planter</x:v>
+        <x:v>tree</x:v>
       </x:c>
       <x:c r="D48" s="7" t="n">
-        <x:v>32</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="E48" s="7" t="n">
         <x:v>575</x:v>
       </x:c>
       <x:c r="F48" s="7" t="n">
-        <x:v>48</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="G48" s="7" t="n">
-        <x:v>48</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="H48" s="7" t="n">
         <x:v>3</x:v>
@@ -1540,25 +1540,25 @@
     </x:row>
     <x:row r="49" ht="15" hidden="0" customHeight="1">
       <x:c r="A49" s="7" t="n">
-        <x:v>44</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="B49" s="7" t="n">
-        <x:v>11</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="C49" s="2" t="str">
-        <x:v>tree</x:v>
+        <x:v>planter</x:v>
       </x:c>
       <x:c r="D49" s="7" t="n">
-        <x:v>84</x:v>
+        <x:v>330</x:v>
       </x:c>
       <x:c r="E49" s="7" t="n">
-        <x:v>571</x:v>
+        <x:v>575</x:v>
       </x:c>
       <x:c r="F49" s="7" t="n">
-        <x:v>40</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="G49" s="7" t="n">
-        <x:v>56</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="H49" s="7" t="n">
         <x:v>3</x:v>
@@ -1566,51 +1566,51 @@
     </x:row>
     <x:row r="50" ht="15" hidden="0" customHeight="1">
       <x:c r="A50" s="7" t="n">
-        <x:v>45</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="B50" s="7" t="n">
-        <x:v>12</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="C50" s="2" t="str">
-        <x:v>planter</x:v>
+        <x:v>tree</x:v>
       </x:c>
       <x:c r="D50" s="7" t="n">
-        <x:v>32</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="E50" s="7" t="n">
-        <x:v>575</x:v>
+        <x:v>115</x:v>
       </x:c>
       <x:c r="F50" s="7" t="n">
-        <x:v>48</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="G50" s="7" t="n">
-        <x:v>48</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="H50" s="7" t="n">
-        <x:v>3</x:v>
+        <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="51" ht="15" hidden="0" customHeight="1">
       <x:c r="A51" s="7" t="n">
-        <x:v>46</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="B51" s="7" t="n">
         <x:v>13</x:v>
       </x:c>
       <x:c r="C51" s="2" t="str">
-        <x:v>tree</x:v>
+        <x:v>planter</x:v>
       </x:c>
       <x:c r="D51" s="7" t="n">
-        <x:v>30</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="E51" s="7" t="n">
         <x:v>115</x:v>
       </x:c>
       <x:c r="F51" s="7" t="n">
-        <x:v>40</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="G51" s="7" t="n">
-        <x:v>56</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="H51" s="7" t="n">
         <x:v>1</x:v>
@@ -1618,7 +1618,7 @@
     </x:row>
     <x:row r="52" ht="15" hidden="0" customHeight="1">
       <x:c r="A52" s="7" t="n">
-        <x:v>47</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="B52" s="7" t="n">
         <x:v>13</x:v>
@@ -1627,10 +1627,10 @@
         <x:v>planter</x:v>
       </x:c>
       <x:c r="D52" s="7" t="n">
-        <x:v>80</x:v>
+        <x:v>350</x:v>
       </x:c>
       <x:c r="E52" s="7" t="n">
-        <x:v>120</x:v>
+        <x:v>535</x:v>
       </x:c>
       <x:c r="F52" s="7" t="n">
         <x:v>48</x:v>
@@ -1639,82 +1639,82 @@
         <x:v>48</x:v>
       </x:c>
       <x:c r="H52" s="7" t="n">
-        <x:v>1</x:v>
+        <x:v>6</x:v>
       </x:c>
     </x:row>
     <x:row r="53" ht="15" hidden="0" customHeight="1">
       <x:c r="A53" s="7" t="n">
-        <x:v>48</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="B53" s="7" t="n">
-        <x:v>13</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="C53" s="2" t="str">
-        <x:v>planter</x:v>
+        <x:v>tree</x:v>
       </x:c>
       <x:c r="D53" s="7" t="n">
-        <x:v>354</x:v>
+        <x:v>350</x:v>
       </x:c>
       <x:c r="E53" s="7" t="n">
-        <x:v>330</x:v>
+        <x:v>115</x:v>
       </x:c>
       <x:c r="F53" s="7" t="n">
-        <x:v>48</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="G53" s="7" t="n">
-        <x:v>48</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="H53" s="7" t="n">
-        <x:v>6</x:v>
+        <x:v>2</x:v>
       </x:c>
     </x:row>
     <x:row r="54" ht="15" hidden="0" customHeight="1">
       <x:c r="A54" s="7" t="n">
-        <x:v>49</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="B54" s="7" t="n">
         <x:v>14</x:v>
       </x:c>
       <x:c r="C54" s="2" t="str">
-        <x:v>tree</x:v>
+        <x:v>planter</x:v>
       </x:c>
       <x:c r="D54" s="7" t="n">
-        <x:v>355</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="E54" s="7" t="n">
-        <x:v>115</x:v>
+        <x:v>575</x:v>
       </x:c>
       <x:c r="F54" s="7" t="n">
-        <x:v>40</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="G54" s="7" t="n">
-        <x:v>56</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="H54" s="7" t="n">
-        <x:v>2</x:v>
+        <x:v>3</x:v>
       </x:c>
     </x:row>
     <x:row r="55" ht="15" hidden="0" customHeight="1">
       <x:c r="A55" s="7" t="n">
-        <x:v>50</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="B55" s="7" t="n">
         <x:v>14</x:v>
       </x:c>
       <x:c r="C55" s="2" t="str">
-        <x:v>planter</x:v>
+        <x:v>tree</x:v>
       </x:c>
       <x:c r="D55" s="7" t="n">
-        <x:v>32</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="E55" s="7" t="n">
         <x:v>575</x:v>
       </x:c>
       <x:c r="F55" s="7" t="n">
-        <x:v>48</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="G55" s="7" t="n">
-        <x:v>48</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="H55" s="7" t="n">
         <x:v>3</x:v>
@@ -1722,25 +1722,25 @@
     </x:row>
     <x:row r="56" ht="15" hidden="0" customHeight="1">
       <x:c r="A56" s="7" t="n">
-        <x:v>51</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="B56" s="7" t="n">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="C56" s="2" t="str">
-        <x:v>tree</x:v>
+        <x:v>planter</x:v>
       </x:c>
       <x:c r="D56" s="7" t="n">
-        <x:v>84</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="E56" s="7" t="n">
-        <x:v>571</x:v>
+        <x:v>575</x:v>
       </x:c>
       <x:c r="F56" s="7" t="n">
-        <x:v>40</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="G56" s="7" t="n">
-        <x:v>56</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="H56" s="7" t="n">
         <x:v>3</x:v>
@@ -1748,51 +1748,51 @@
     </x:row>
     <x:row r="57" ht="15" hidden="0" customHeight="1">
       <x:c r="A57" s="7" t="n">
-        <x:v>52</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="B57" s="7" t="n">
-        <x:v>15</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="C57" s="2" t="str">
-        <x:v>planter</x:v>
+        <x:v>tree</x:v>
       </x:c>
       <x:c r="D57" s="7" t="n">
-        <x:v>32</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="E57" s="7" t="n">
-        <x:v>575</x:v>
+        <x:v>115</x:v>
       </x:c>
       <x:c r="F57" s="7" t="n">
-        <x:v>48</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="G57" s="7" t="n">
-        <x:v>48</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="H57" s="7" t="n">
-        <x:v>3</x:v>
+        <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="58" ht="15" hidden="0" customHeight="1">
       <x:c r="A58" s="7" t="n">
-        <x:v>53</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="B58" s="7" t="n">
         <x:v>17</x:v>
       </x:c>
       <x:c r="C58" s="2" t="str">
-        <x:v>tree</x:v>
+        <x:v>planter</x:v>
       </x:c>
       <x:c r="D58" s="7" t="n">
-        <x:v>30</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="E58" s="7" t="n">
         <x:v>115</x:v>
       </x:c>
       <x:c r="F58" s="7" t="n">
-        <x:v>40</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="G58" s="7" t="n">
-        <x:v>56</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="H58" s="7" t="n">
         <x:v>1</x:v>
@@ -1800,19 +1800,19 @@
     </x:row>
     <x:row r="59" ht="15" hidden="0" customHeight="1">
       <x:c r="A59" s="7" t="n">
-        <x:v>54</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="B59" s="7" t="n">
-        <x:v>17</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C59" s="2" t="str">
         <x:v>planter</x:v>
       </x:c>
       <x:c r="D59" s="7" t="n">
-        <x:v>80</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="E59" s="7" t="n">
-        <x:v>120</x:v>
+        <x:v>575</x:v>
       </x:c>
       <x:c r="F59" s="7" t="n">
         <x:v>48</x:v>
@@ -1821,12 +1821,12 @@
         <x:v>48</x:v>
       </x:c>
       <x:c r="H59" s="7" t="n">
-        <x:v>1</x:v>
+        <x:v>3</x:v>
       </x:c>
     </x:row>
     <x:row r="60" ht="15" hidden="0" customHeight="1">
       <x:c r="A60" s="7" t="n">
-        <x:v>55</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="B60" s="7" t="n">
         <x:v>19</x:v>
@@ -1835,10 +1835,10 @@
         <x:v>planter</x:v>
       </x:c>
       <x:c r="D60" s="7" t="n">
-        <x:v>32</x:v>
+        <x:v>350</x:v>
       </x:c>
       <x:c r="E60" s="7" t="n">
-        <x:v>575</x:v>
+        <x:v>325</x:v>
       </x:c>
       <x:c r="F60" s="7" t="n">
         <x:v>48</x:v>
@@ -1847,24 +1847,24 @@
         <x:v>48</x:v>
       </x:c>
       <x:c r="H60" s="7" t="n">
-        <x:v>3</x:v>
+        <x:v>6</x:v>
       </x:c>
     </x:row>
     <x:row r="61" ht="15" hidden="0" customHeight="1">
       <x:c r="A61" s="7" t="n">
-        <x:v>56</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="B61" s="7" t="n">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="C61" s="2" t="str">
         <x:v>planter</x:v>
       </x:c>
       <x:c r="D61" s="7" t="n">
-        <x:v>354</x:v>
+        <x:v>350</x:v>
       </x:c>
       <x:c r="E61" s="7" t="n">
-        <x:v>330</x:v>
+        <x:v>315</x:v>
       </x:c>
       <x:c r="F61" s="7" t="n">
         <x:v>48</x:v>
@@ -1878,19 +1878,19 @@
     </x:row>
     <x:row r="62" ht="15" hidden="0" customHeight="1">
       <x:c r="A62" s="7" t="n">
-        <x:v>57</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="B62" s="7" t="n">
-        <x:v>20</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="C62" s="2" t="str">
         <x:v>planter</x:v>
       </x:c>
       <x:c r="D62" s="7" t="n">
-        <x:v>354</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="E62" s="7" t="n">
-        <x:v>330</x:v>
+        <x:v>115</x:v>
       </x:c>
       <x:c r="F62" s="7" t="n">
         <x:v>48</x:v>
@@ -1899,30 +1899,30 @@
         <x:v>48</x:v>
       </x:c>
       <x:c r="H62" s="7" t="n">
-        <x:v>6</x:v>
+        <x:v>4</x:v>
       </x:c>
     </x:row>
     <x:row r="63">
       <x:c r="A63" t="n">
-        <x:v>58</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="B63" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="C63" t="str">
-        <x:v>planter</x:v>
+        <x:v>tree</x:v>
       </x:c>
       <x:c r="D63" t="n">
-        <x:v>104</x:v>
+        <x:v>320</x:v>
       </x:c>
       <x:c r="E63" t="n">
-        <x:v>116</x:v>
+        <x:v>115</x:v>
       </x:c>
       <x:c r="F63" t="n">
-        <x:v>48</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="G63" t="n">
-        <x:v>48</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="H63" t="n">
         <x:v>4</x:v>
@@ -1930,19 +1930,19 @@
     </x:row>
     <x:row r="64">
       <x:c r="A64" t="n">
-        <x:v>59</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="B64" t="n">
-        <x:v>1</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="C64" t="str">
         <x:v>tree</x:v>
       </x:c>
       <x:c r="D64" t="n">
-        <x:v>310</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="E64" t="n">
-        <x:v>119</x:v>
+        <x:v>550</x:v>
       </x:c>
       <x:c r="F64" t="n">
         <x:v>40</x:v>
@@ -1951,30 +1951,30 @@
         <x:v>56</x:v>
       </x:c>
       <x:c r="H64" t="n">
-        <x:v>4</x:v>
+        <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="65">
       <x:c r="A65" t="n">
-        <x:v>60</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="B65" t="n">
         <x:v>21</x:v>
       </x:c>
       <x:c r="C65" t="str">
-        <x:v>tree</x:v>
+        <x:v>planter</x:v>
       </x:c>
       <x:c r="D65" t="n">
-        <x:v>64</x:v>
+        <x:v>116</x:v>
       </x:c>
       <x:c r="E65" t="n">
-        <x:v>550</x:v>
+        <x:v>554</x:v>
       </x:c>
       <x:c r="F65" t="n">
-        <x:v>40</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="G65" t="n">
-        <x:v>56</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="H65" t="n">
         <x:v>1</x:v>
@@ -1982,51 +1982,51 @@
     </x:row>
     <x:row r="66">
       <x:c r="A66" t="n">
-        <x:v>61</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="B66" t="n">
         <x:v>21</x:v>
       </x:c>
       <x:c r="C66" t="str">
-        <x:v>planter</x:v>
+        <x:v>tree</x:v>
       </x:c>
       <x:c r="D66" t="n">
-        <x:v>116</x:v>
+        <x:v>352</x:v>
       </x:c>
       <x:c r="E66" t="n">
-        <x:v>554</x:v>
+        <x:v>370</x:v>
       </x:c>
       <x:c r="F66" t="n">
-        <x:v>48</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="G66" t="n">
-        <x:v>48</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="H66" t="n">
-        <x:v>1</x:v>
+        <x:v>2</x:v>
       </x:c>
     </x:row>
     <x:row r="67">
       <x:c r="A67" t="n">
-        <x:v>62</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="B67" t="n">
         <x:v>21</x:v>
       </x:c>
       <x:c r="C67" t="str">
-        <x:v>tree</x:v>
+        <x:v>planter</x:v>
       </x:c>
       <x:c r="D67" t="n">
         <x:v>352</x:v>
       </x:c>
       <x:c r="E67" t="n">
-        <x:v>370</x:v>
+        <x:v>434</x:v>
       </x:c>
       <x:c r="F67" t="n">
-        <x:v>40</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="G67" t="n">
-        <x:v>56</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="H67" t="n">
         <x:v>2</x:v>
@@ -2034,55 +2034,39 @@
     </x:row>
     <x:row r="68">
       <x:c r="A68" t="n">
-        <x:v>63</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="B68" t="n">
         <x:v>21</x:v>
       </x:c>
       <x:c r="C68" t="str">
-        <x:v>planter</x:v>
+        <x:v>tree</x:v>
       </x:c>
       <x:c r="D68" t="n">
-        <x:v>352</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="E68" t="n">
-        <x:v>434</x:v>
+        <x:v>212</x:v>
       </x:c>
       <x:c r="F68" t="n">
-        <x:v>48</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="G68" t="n">
-        <x:v>48</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="H68" t="n">
-        <x:v>2</x:v>
+        <x:v>3</x:v>
       </x:c>
     </x:row>
     <x:row r="69">
-      <x:c r="A69" t="n">
-        <x:v>64</x:v>
-      </x:c>
-      <x:c r="B69" t="n">
-        <x:v>21</x:v>
-      </x:c>
-      <x:c r="C69" t="str">
-        <x:v>tree</x:v>
-      </x:c>
-      <x:c r="D69" t="n">
-        <x:v>52</x:v>
-      </x:c>
-      <x:c r="E69" t="n">
-        <x:v>212</x:v>
-      </x:c>
-      <x:c r="F69" t="n">
-        <x:v>40</x:v>
-      </x:c>
-      <x:c r="G69" t="n">
-        <x:v>56</x:v>
-      </x:c>
-      <x:c r="H69" t="n">
-        <x:v>3</x:v>
-      </x:c>
+      <x:c r="A69"/>
+      <x:c r="B69"/>
+      <x:c r="C69"/>
+      <x:c r="D69"/>
+      <x:c r="E69"/>
+      <x:c r="F69"/>
+      <x:c r="G69"/>
+      <x:c r="H69"/>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/design/tables/Decoration.xlsx
+++ b/design/tables/Decoration.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Decoration" sheetId="1" r:id="R372ba71c7891410a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Decoration" sheetId="1" r:id="Rc697b517fd964fce"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -509,10 +509,10 @@
         <x:v>planter</x:v>
       </x:c>
       <x:c r="D9" s="7" t="n">
-        <x:v>350</x:v>
+        <x:v>360</x:v>
       </x:c>
       <x:c r="E9" s="7" t="n">
-        <x:v>275</x:v>
+        <x:v>205</x:v>
       </x:c>
       <x:c r="F9" s="7" t="n">
         <x:v>48</x:v>
@@ -616,7 +616,7 @@
         <x:v>190</x:v>
       </x:c>
       <x:c r="E13" s="7" t="n">
-        <x:v>575</x:v>
+        <x:v>565</x:v>
       </x:c>
       <x:c r="F13" s="7" t="n">
         <x:v>48</x:v>
@@ -642,7 +642,7 @@
         <x:v>350</x:v>
       </x:c>
       <x:c r="E14" s="7" t="n">
-        <x:v>105</x:v>
+        <x:v>285</x:v>
       </x:c>
       <x:c r="F14" s="7" t="n">
         <x:v>48</x:v>
@@ -665,10 +665,10 @@
         <x:v>planter</x:v>
       </x:c>
       <x:c r="D15" s="7" t="n">
-        <x:v>240</x:v>
+        <x:v>350</x:v>
       </x:c>
       <x:c r="E15" s="7" t="n">
-        <x:v>575</x:v>
+        <x:v>465</x:v>
       </x:c>
       <x:c r="F15" s="7" t="n">
         <x:v>48</x:v>
@@ -743,7 +743,7 @@
         <x:v>tree</x:v>
       </x:c>
       <x:c r="D18" s="7" t="n">
-        <x:v>350</x:v>
+        <x:v>190</x:v>
       </x:c>
       <x:c r="E18" s="7" t="n">
         <x:v>125</x:v>
@@ -769,7 +769,7 @@
         <x:v>planter</x:v>
       </x:c>
       <x:c r="D19" s="7" t="n">
-        <x:v>170</x:v>
+        <x:v>180</x:v>
       </x:c>
       <x:c r="E19" s="7" t="n">
         <x:v>565</x:v>
@@ -873,7 +873,7 @@
         <x:v>planter</x:v>
       </x:c>
       <x:c r="D23" s="7" t="n">
-        <x:v>350</x:v>
+        <x:v>360</x:v>
       </x:c>
       <x:c r="E23" s="7" t="n">
         <x:v>205</x:v>
@@ -899,7 +899,7 @@
         <x:v>tree</x:v>
       </x:c>
       <x:c r="D24" s="7" t="n">
-        <x:v>50</x:v>
+        <x:v>260</x:v>
       </x:c>
       <x:c r="E24" s="7" t="n">
         <x:v>115</x:v>
@@ -925,7 +925,7 @@
         <x:v>planter</x:v>
       </x:c>
       <x:c r="D25" s="7" t="n">
-        <x:v>110</x:v>
+        <x:v>310</x:v>
       </x:c>
       <x:c r="E25" s="7" t="n">
         <x:v>125</x:v>
@@ -951,7 +951,7 @@
         <x:v>tree</x:v>
       </x:c>
       <x:c r="D26" s="7" t="n">
-        <x:v>280</x:v>
+        <x:v>360</x:v>
       </x:c>
       <x:c r="E26" s="7" t="n">
         <x:v>135</x:v>
@@ -977,10 +977,10 @@
         <x:v>planter</x:v>
       </x:c>
       <x:c r="D27" s="7" t="n">
-        <x:v>340</x:v>
+        <x:v>290</x:v>
       </x:c>
       <x:c r="E27" s="7" t="n">
-        <x:v>135</x:v>
+        <x:v>545</x:v>
       </x:c>
       <x:c r="F27" s="7" t="n">
         <x:v>48</x:v>
@@ -1003,10 +1003,10 @@
         <x:v>planter</x:v>
       </x:c>
       <x:c r="D28" s="7" t="n">
-        <x:v>30</x:v>
+        <x:v>350</x:v>
       </x:c>
       <x:c r="E28" s="7" t="n">
-        <x:v>575</x:v>
+        <x:v>565</x:v>
       </x:c>
       <x:c r="F28" s="7" t="n">
         <x:v>48</x:v>
@@ -1029,10 +1029,10 @@
         <x:v>tree</x:v>
       </x:c>
       <x:c r="D29" s="7" t="n">
-        <x:v>340</x:v>
+        <x:v>350</x:v>
       </x:c>
       <x:c r="E29" s="7" t="n">
-        <x:v>285</x:v>
+        <x:v>205</x:v>
       </x:c>
       <x:c r="F29" s="7" t="n">
         <x:v>40</x:v>
@@ -1058,7 +1058,7 @@
         <x:v>360</x:v>
       </x:c>
       <x:c r="E30" s="7" t="n">
-        <x:v>225</x:v>
+        <x:v>495</x:v>
       </x:c>
       <x:c r="F30" s="7" t="n">
         <x:v>48</x:v>
@@ -1084,7 +1084,7 @@
         <x:v>30</x:v>
       </x:c>
       <x:c r="E31" s="7" t="n">
-        <x:v>485</x:v>
+        <x:v>455</x:v>
       </x:c>
       <x:c r="F31" s="7" t="n">
         <x:v>40</x:v>
@@ -1110,7 +1110,7 @@
         <x:v>280</x:v>
       </x:c>
       <x:c r="E32" s="7" t="n">
-        <x:v>575</x:v>
+        <x:v>565</x:v>
       </x:c>
       <x:c r="F32" s="7" t="n">
         <x:v>48</x:v>
@@ -1185,10 +1185,10 @@
         <x:v>tree</x:v>
       </x:c>
       <x:c r="D35" s="7" t="n">
-        <x:v>360</x:v>
+        <x:v>190</x:v>
       </x:c>
       <x:c r="E35" s="7" t="n">
-        <x:v>365</x:v>
+        <x:v>485</x:v>
       </x:c>
       <x:c r="F35" s="7" t="n">
         <x:v>40</x:v>
@@ -1214,7 +1214,7 @@
         <x:v>130</x:v>
       </x:c>
       <x:c r="E36" s="7" t="n">
-        <x:v>145</x:v>
+        <x:v>125</x:v>
       </x:c>
       <x:c r="F36" s="7" t="n">
         <x:v>48</x:v>
@@ -1344,7 +1344,7 @@
         <x:v>50</x:v>
       </x:c>
       <x:c r="E41" s="7" t="n">
-        <x:v>195</x:v>
+        <x:v>205</x:v>
       </x:c>
       <x:c r="F41" s="7" t="n">
         <x:v>48</x:v>
@@ -1445,10 +1445,10 @@
         <x:v>planter</x:v>
       </x:c>
       <x:c r="D45" s="7" t="n">
-        <x:v>350</x:v>
+        <x:v>180</x:v>
       </x:c>
       <x:c r="E45" s="7" t="n">
-        <x:v>105</x:v>
+        <x:v>115</x:v>
       </x:c>
       <x:c r="F45" s="7" t="n">
         <x:v>48</x:v>
@@ -1471,10 +1471,10 @@
         <x:v>tree</x:v>
       </x:c>
       <x:c r="D46" s="7" t="n">
-        <x:v>50</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="E46" s="7" t="n">
-        <x:v>105</x:v>
+        <x:v>115</x:v>
       </x:c>
       <x:c r="F46" s="7" t="n">
         <x:v>40</x:v>
@@ -1500,7 +1500,7 @@
         <x:v>30</x:v>
       </x:c>
       <x:c r="E47" s="7" t="n">
-        <x:v>575</x:v>
+        <x:v>565</x:v>
       </x:c>
       <x:c r="F47" s="7" t="n">
         <x:v>48</x:v>
@@ -1526,7 +1526,7 @@
         <x:v>90</x:v>
       </x:c>
       <x:c r="E48" s="7" t="n">
-        <x:v>575</x:v>
+        <x:v>565</x:v>
       </x:c>
       <x:c r="F48" s="7" t="n">
         <x:v>40</x:v>
@@ -1552,7 +1552,7 @@
         <x:v>330</x:v>
       </x:c>
       <x:c r="E49" s="7" t="n">
-        <x:v>575</x:v>
+        <x:v>565</x:v>
       </x:c>
       <x:c r="F49" s="7" t="n">
         <x:v>48</x:v>
@@ -1627,7 +1627,7 @@
         <x:v>planter</x:v>
       </x:c>
       <x:c r="D52" s="7" t="n">
-        <x:v>350</x:v>
+        <x:v>360</x:v>
       </x:c>
       <x:c r="E52" s="7" t="n">
         <x:v>535</x:v>
@@ -1682,7 +1682,7 @@
         <x:v>30</x:v>
       </x:c>
       <x:c r="E54" s="7" t="n">
-        <x:v>575</x:v>
+        <x:v>565</x:v>
       </x:c>
       <x:c r="F54" s="7" t="n">
         <x:v>48</x:v>
@@ -1708,7 +1708,7 @@
         <x:v>90</x:v>
       </x:c>
       <x:c r="E55" s="7" t="n">
-        <x:v>575</x:v>
+        <x:v>565</x:v>
       </x:c>
       <x:c r="F55" s="7" t="n">
         <x:v>40</x:v>
@@ -1734,7 +1734,7 @@
         <x:v>30</x:v>
       </x:c>
       <x:c r="E56" s="7" t="n">
-        <x:v>575</x:v>
+        <x:v>565</x:v>
       </x:c>
       <x:c r="F56" s="7" t="n">
         <x:v>48</x:v>
@@ -1812,7 +1812,7 @@
         <x:v>30</x:v>
       </x:c>
       <x:c r="E59" s="7" t="n">
-        <x:v>575</x:v>
+        <x:v>565</x:v>
       </x:c>
       <x:c r="F59" s="7" t="n">
         <x:v>48</x:v>
@@ -1835,7 +1835,7 @@
         <x:v>planter</x:v>
       </x:c>
       <x:c r="D60" s="7" t="n">
-        <x:v>350</x:v>
+        <x:v>360</x:v>
       </x:c>
       <x:c r="E60" s="7" t="n">
         <x:v>325</x:v>
@@ -1861,10 +1861,10 @@
         <x:v>planter</x:v>
       </x:c>
       <x:c r="D61" s="7" t="n">
-        <x:v>350</x:v>
+        <x:v>360</x:v>
       </x:c>
       <x:c r="E61" s="7" t="n">
-        <x:v>315</x:v>
+        <x:v>495</x:v>
       </x:c>
       <x:c r="F61" s="7" t="n">
         <x:v>48</x:v>
@@ -1887,7 +1887,7 @@
         <x:v>planter</x:v>
       </x:c>
       <x:c r="D62" s="7" t="n">
-        <x:v>100</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="E62" s="7" t="n">
         <x:v>115</x:v>
